--- a/data/trans_orig/P1403-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2007</t>
+          <t>Población con diagnóstico de hipertensión en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490185</t>
+          <t>490135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>460179</t>
+          <t>460467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466711</t>
+          <t>466706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>953372</t>
+          <t>953092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960635</t>
+          <t>960624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19228</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>728581</t>
+          <t>728337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608715</t>
+          <t>608369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620762</t>
+          <t>620645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1341754</t>
+          <t>1341957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355230</t>
+          <t>1355670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>29683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38542</t>
+          <t>39014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65339</t>
+          <t>66041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608187</t>
+          <t>608985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625439</t>
+          <t>625970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647294</t>
+          <t>647344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>669076</t>
+          <t>668906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1263073</t>
+          <t>1262371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289870</t>
+          <t>1289398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57313</t>
+          <t>55838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>89382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45386</t>
+          <t>43640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74460</t>
+          <t>72227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108716</t>
+          <t>109750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148776</t>
+          <t>151698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430483</t>
+          <t>429765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>461834</t>
+          <t>463309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441182</t>
+          <t>443415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470256</t>
+          <t>472002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886013</t>
+          <t>883091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>926073</t>
+          <t>925039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>102100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136374</t>
+          <t>138218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109737</t>
+          <t>109438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144772</t>
+          <t>145047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220517</t>
+          <t>219797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273633</t>
+          <t>271081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250336</t>
+          <t>248492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285047</t>
+          <t>284610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259214</t>
+          <t>258939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>294249</t>
+          <t>294548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517063</t>
+          <t>519615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570179</t>
+          <t>570899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98409</t>
+          <t>99490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131708</t>
+          <t>131071</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>140070</t>
+          <t>141598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172749</t>
+          <t>175132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>247219</t>
+          <t>245920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>292238</t>
+          <t>294054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160875</t>
+          <t>161512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194174</t>
+          <t>193093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170185</t>
+          <t>167802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202864</t>
+          <t>201336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343279</t>
+          <t>341463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>388298</t>
+          <t>389597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85133</t>
+          <t>86300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115016</t>
+          <t>115591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169350</t>
+          <t>170586</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207506</t>
+          <t>208101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260135</t>
+          <t>263342</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309076</t>
+          <t>311994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>94292</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124750</t>
+          <t>123583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>125807</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164558</t>
+          <t>163322</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>234715</t>
+          <t>231797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283656</t>
+          <t>280449</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>388336</t>
+          <t>391893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>465680</t>
+          <t>469366</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>528587</t>
+          <t>533039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>619019</t>
+          <t>616523</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>945675</t>
+          <t>948521</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1059189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2810863</t>
+          <t>2807177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2888207</t>
+          <t>2884650</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2760178</t>
+          <t>2762674</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2850610</t>
+          <t>2846158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5595396</t>
+          <t>5596552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5710066</t>
+          <t>5707220</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2012</t>
+          <t>Población con diagnóstico de hipertensión en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,62 +3747,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5326</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449177</t>
+          <t>449321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879050</t>
+          <t>879873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673254</t>
+          <t>674097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684047</t>
+          <t>684313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>591791</t>
+          <t>591719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606395</t>
+          <t>605545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270211</t>
+          <t>1270711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287800</t>
+          <t>1287960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45637</t>
+          <t>44924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>76544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634667</t>
+          <t>636298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658813</t>
+          <t>659459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>672320</t>
+          <t>673025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>692802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313904</t>
+          <t>1314893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1345800</t>
+          <t>1346513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57982</t>
+          <t>56244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91791</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>66351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102237</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131648</t>
+          <t>133252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181825</t>
+          <t>180814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522826</t>
+          <t>524456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556635</t>
+          <t>558373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512027</t>
+          <t>512794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>546832</t>
+          <t>547913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1047055</t>
+          <t>1048066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1097232</t>
+          <t>1095628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132537</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171459</t>
+          <t>173181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152662</t>
+          <t>154323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194734</t>
+          <t>196831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294434</t>
+          <t>296394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>353512</t>
+          <t>356481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257970</t>
+          <t>256248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296892</t>
+          <t>297674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253066</t>
+          <t>250969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295138</t>
+          <t>293477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>523717</t>
+          <t>520748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>582795</t>
+          <t>580835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143092</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178933</t>
+          <t>180288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>181743</t>
+          <t>183827</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>220762</t>
+          <t>222289</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>339171</t>
+          <t>337162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>391191</t>
+          <t>389380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130853</t>
+          <t>129498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166694</t>
+          <t>166842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133234</t>
+          <t>131707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172253</t>
+          <t>170169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>272591</t>
+          <t>274402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>324611</t>
+          <t>326620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132021</t>
+          <t>132267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165564</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>232521</t>
+          <t>231183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270981</t>
+          <t>269302</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375805</t>
+          <t>377763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425789</t>
+          <t>427669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84287</t>
+          <t>84374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117830</t>
+          <t>117584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116889</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155349</t>
+          <t>156687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>211932</t>
+          <t>210052</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261916</t>
+          <t>259958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>529684</t>
+          <t>529427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>631117</t>
+          <t>618780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>695616</t>
+          <t>691577</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>796065</t>
+          <t>792112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1249465</t>
+          <t>1257558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1387466</t>
+          <t>1382834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2795662</t>
+          <t>2807999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2897095</t>
+          <t>2897352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2757925</t>
+          <t>2761878</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2858374</t>
+          <t>2862413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5593303</t>
+          <t>5597935</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5731304</t>
+          <t>5723211</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2016</t>
+          <t>Población con diagnóstico de hipertensión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411492</t>
+          <t>412601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391224</t>
+          <t>391231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>806901</t>
+          <t>806900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575396</t>
+          <t>576015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587579</t>
+          <t>587738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556885</t>
+          <t>556873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1136247</t>
+          <t>1136605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150089</t>
+          <t>1150096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,82 +7392,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16275</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9685</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25488</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>39462</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>29273</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>54510</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16275</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25376</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>39462</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>29103</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>52880</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635402</t>
+          <t>635184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654362</t>
+          <t>654513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,82 +7505,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>645111</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>635898</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>651701</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1291021</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1275973</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1301210</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>645111</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>636010</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>651879</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1291021</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1277603</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1301380</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71514</t>
+          <t>71518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106628</t>
+          <t>109406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44449</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124025</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169983</t>
+          <t>172619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539420</t>
+          <t>536642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574534</t>
+          <t>574530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573695</t>
+          <t>575652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604628</t>
+          <t>604128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1125142</t>
+          <t>1122506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1171100</t>
+          <t>1171348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102568</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143754</t>
+          <t>140878</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127560</t>
+          <t>125356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170238</t>
+          <t>169506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236746</t>
+          <t>240351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301066</t>
+          <t>298425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334164</t>
+          <t>337040</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375350</t>
+          <t>377973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326611</t>
+          <t>327343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>369289</t>
+          <t>371493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>673701</t>
+          <t>676342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738021</t>
+          <t>734416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119728</t>
+          <t>120433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156864</t>
+          <t>154331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154810</t>
+          <t>154862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193996</t>
+          <t>194956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284367</t>
+          <t>285758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337724</t>
+          <t>338574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177466</t>
+          <t>179999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214602</t>
+          <t>213897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183766</t>
+          <t>182806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222952</t>
+          <t>222900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>374368</t>
+          <t>373518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>427725</t>
+          <t>426334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>122290</t>
+          <t>124715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152558</t>
+          <t>152932</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208391</t>
+          <t>205087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251664</t>
+          <t>249931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>340173</t>
+          <t>339829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393788</t>
+          <t>393680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104440</t>
+          <t>104066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134708</t>
+          <t>132283</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148505</t>
+          <t>150238</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>191778</t>
+          <t>195082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263379</t>
+          <t>263487</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>316994</t>
+          <t>317338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>475498</t>
+          <t>473573</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>556729</t>
+          <t>555243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>583550</t>
+          <t>582971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>682867</t>
+          <t>676205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1081724</t>
+          <t>1077061</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1206179</t>
+          <t>1201718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2837621</t>
+          <t>2839107</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2918852</t>
+          <t>2920777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2861675</t>
+          <t>2868337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2960992</t>
+          <t>2961571</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5732713</t>
+          <t>5737174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5857168</t>
+          <t>5861831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2023</t>
+          <t>Población con diagnóstico de hipertensión en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399086</t>
+          <t>399134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304767</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703339</t>
+          <t>702986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712889</t>
+          <t>712633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413008</t>
+          <t>412672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422211</t>
+          <t>422020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500469</t>
+          <t>500088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509928</t>
+          <t>510000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917460</t>
+          <t>918230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930357</t>
+          <t>930631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504218</t>
+          <t>504707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522387</t>
+          <t>522711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521459</t>
+          <t>521438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533108</t>
+          <t>533364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031425</t>
+          <t>1031259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053227</t>
+          <t>1053914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46730</t>
+          <t>47351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157464</t>
+          <t>157714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73250</t>
+          <t>74551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109981</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108686</t>
+          <t>124341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245638</t>
+          <t>248081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>730322</t>
+          <t>730072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841056</t>
+          <t>840435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602517</t>
+          <t>601319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639248</t>
+          <t>637947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1354647</t>
+          <t>1352204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1491599</t>
+          <t>1475944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147353</t>
+          <t>144872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187604</t>
+          <t>185847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128380</t>
+          <t>128920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157611</t>
+          <t>159729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284624</t>
+          <t>284496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334022</t>
+          <t>337185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372633</t>
+          <t>374390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>412884</t>
+          <t>415365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386498</t>
+          <t>384380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415729</t>
+          <t>415189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>770324</t>
+          <t>767161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>819722</t>
+          <t>819850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154287</t>
+          <t>154093</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>183633</t>
+          <t>185824</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275805</t>
+          <t>276067</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>522356</t>
+          <t>525104</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>443997</t>
+          <t>441921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>752390</t>
+          <t>766957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182457</t>
+          <t>180266</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211803</t>
+          <t>211997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84825</t>
+          <t>82077</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331376</t>
+          <t>331114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>220881</t>
+          <t>206314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529274</t>
+          <t>531350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140982</t>
+          <t>140494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166758</t>
+          <t>166808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261201</t>
+          <t>259886</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287714</t>
+          <t>288691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408558</t>
+          <t>408056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446883</t>
+          <t>448642</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116001</t>
+          <t>115951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141777</t>
+          <t>142265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137191</t>
+          <t>136214</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>163704</t>
+          <t>165019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260781</t>
+          <t>259022</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299106</t>
+          <t>299608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>491642</t>
+          <t>483909</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>687285</t>
+          <t>689114</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>742025</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1482576</t>
+          <t>1477015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1339617</t>
+          <t>1335900</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2252052</t>
+          <t>2124866</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2768280</t>
+          <t>2766451</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2963923</t>
+          <t>2971656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2172620</t>
+          <t>2178181</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2907191</t>
+          <t>2913171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4858709</t>
+          <t>4985895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5771144</t>
+          <t>5774861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1403-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490135</t>
+          <t>490101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>460467</t>
+          <t>459929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466706</t>
+          <t>467489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>953092</t>
+          <t>952064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960624</t>
+          <t>960618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>728337</t>
+          <t>729007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608369</t>
+          <t>608572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620645</t>
+          <t>620683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1341957</t>
+          <t>1340691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355670</t>
+          <t>1354994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39014</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66041</t>
+          <t>66114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608985</t>
+          <t>607717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625970</t>
+          <t>625955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647344</t>
+          <t>645679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>668906</t>
+          <t>668668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262371</t>
+          <t>1262298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289398</t>
+          <t>1290511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55838</t>
+          <t>57462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89382</t>
+          <t>89006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43640</t>
+          <t>43331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72227</t>
+          <t>72416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109750</t>
+          <t>109204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151698</t>
+          <t>152523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>429765</t>
+          <t>430141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>463309</t>
+          <t>461685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443415</t>
+          <t>443226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472002</t>
+          <t>472311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>883091</t>
+          <t>882266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>925039</t>
+          <t>925585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102100</t>
+          <t>102021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138218</t>
+          <t>139385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109438</t>
+          <t>109010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145047</t>
+          <t>146070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>221180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271081</t>
+          <t>271881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>248492</t>
+          <t>247325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284610</t>
+          <t>284689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258939</t>
+          <t>257916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>294548</t>
+          <t>294976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>519615</t>
+          <t>518815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570899</t>
+          <t>569516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99490</t>
+          <t>96830</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131071</t>
+          <t>129678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141598</t>
+          <t>138664</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>173976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>245920</t>
+          <t>247380</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>294054</t>
+          <t>295645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161512</t>
+          <t>162905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193093</t>
+          <t>195753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167802</t>
+          <t>168958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201336</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341463</t>
+          <t>339872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>389597</t>
+          <t>388137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86300</t>
+          <t>83344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115591</t>
+          <t>113074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170586</t>
+          <t>168813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208101</t>
+          <t>207820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263342</t>
+          <t>263203</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311994</t>
+          <t>311523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94292</t>
+          <t>96809</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123583</t>
+          <t>126539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125807</t>
+          <t>126088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>163322</t>
+          <t>165095</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231797</t>
+          <t>232268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280449</t>
+          <t>280588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>391893</t>
+          <t>390835</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>469366</t>
+          <t>467759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>533039</t>
+          <t>533685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>616523</t>
+          <t>618416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>948521</t>
+          <t>934256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1059189</t>
+          <t>1053357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2807177</t>
+          <t>2808784</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2884650</t>
+          <t>2885708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2762674</t>
+          <t>2760781</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2846158</t>
+          <t>2845512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5596552</t>
+          <t>5602384</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5707220</t>
+          <t>5721485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449321</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879873</t>
+          <t>879546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>674097</t>
+          <t>673304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684313</t>
+          <t>684250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>591719</t>
+          <t>592222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605545</t>
+          <t>606215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270711</t>
+          <t>1271011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287960</t>
+          <t>1288079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>48220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36549</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76544</t>
+          <t>78905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636298</t>
+          <t>633643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659459</t>
+          <t>658805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673025</t>
+          <t>672670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>692802</t>
+          <t>693337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314893</t>
+          <t>1312532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1346513</t>
+          <t>1345569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>57500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90161</t>
+          <t>90868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66351</t>
+          <t>67133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101470</t>
+          <t>103086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133252</t>
+          <t>133800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180814</t>
+          <t>182624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>524456</t>
+          <t>523749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>558373</t>
+          <t>557117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512794</t>
+          <t>511178</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>547913</t>
+          <t>547131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1048066</t>
+          <t>1046256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1095628</t>
+          <t>1095080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131755</t>
+          <t>129614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173181</t>
+          <t>172174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>152547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196831</t>
+          <t>196725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>296394</t>
+          <t>295336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356481</t>
+          <t>356319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256248</t>
+          <t>257255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297674</t>
+          <t>299815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>250969</t>
+          <t>251075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>293477</t>
+          <t>295253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>520748</t>
+          <t>520910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>580835</t>
+          <t>581893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142944</t>
+          <t>142566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>180288</t>
+          <t>180148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>185024</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222289</t>
+          <t>222230</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>337162</t>
+          <t>336856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>389380</t>
+          <t>390488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129498</t>
+          <t>129638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166842</t>
+          <t>167220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>131766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>168972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274402</t>
+          <t>273294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>326620</t>
+          <t>326926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132267</t>
+          <t>135210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165477</t>
+          <t>167913</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>231183</t>
+          <t>232862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>269302</t>
+          <t>270474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>377763</t>
+          <t>377353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>427669</t>
+          <t>428648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84374</t>
+          <t>81938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117584</t>
+          <t>114641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118568</t>
+          <t>117396</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>156687</t>
+          <t>155008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>210052</t>
+          <t>209073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259958</t>
+          <t>260368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>529427</t>
+          <t>531292</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>618780</t>
+          <t>625083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>691577</t>
+          <t>695173</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>792112</t>
+          <t>796731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1257558</t>
+          <t>1256085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1382834</t>
+          <t>1389061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2807999</t>
+          <t>2801696</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2897352</t>
+          <t>2895487</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2761878</t>
+          <t>2757259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2862413</t>
+          <t>2858817</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5597935</t>
+          <t>5591708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5723211</t>
+          <t>5724684</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412601</t>
+          <t>412483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391231</t>
+          <t>391230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>806900</t>
+          <t>806904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>576015</t>
+          <t>574753</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587738</t>
+          <t>587856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556873</t>
+          <t>557138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1136605</t>
+          <t>1135802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150096</t>
+          <t>1149597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25488</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>53325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635184</t>
+          <t>633657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654513</t>
+          <t>654108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635898</t>
+          <t>634832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651701</t>
+          <t>651421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1275973</t>
+          <t>1277158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1301210</t>
+          <t>1301619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>68430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109406</t>
+          <t>105020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44949</t>
+          <t>45202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>75497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123777</t>
+          <t>122997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172619</t>
+          <t>170647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>536642</t>
+          <t>541028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574530</t>
+          <t>577618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575652</t>
+          <t>573580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604128</t>
+          <t>603875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122506</t>
+          <t>1124478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1171348</t>
+          <t>1172128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99945</t>
+          <t>100880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140878</t>
+          <t>141583</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125356</t>
+          <t>127678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169506</t>
+          <t>168748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240351</t>
+          <t>238962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298425</t>
+          <t>297204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337040</t>
+          <t>336335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377973</t>
+          <t>377038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327343</t>
+          <t>328101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371493</t>
+          <t>369171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>676342</t>
+          <t>677563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>734416</t>
+          <t>735805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120433</t>
+          <t>119062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154331</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>155700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194956</t>
+          <t>196817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285758</t>
+          <t>284765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338574</t>
+          <t>340534</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179999</t>
+          <t>180504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213897</t>
+          <t>215268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182806</t>
+          <t>180945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222900</t>
+          <t>222062</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>373518</t>
+          <t>371558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>426334</t>
+          <t>427327</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124715</t>
+          <t>123784</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>152225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205087</t>
+          <t>205063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249931</t>
+          <t>251866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>339829</t>
+          <t>341337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393680</t>
+          <t>391848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104066</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>133214</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150238</t>
+          <t>148303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>195082</t>
+          <t>195106</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263487</t>
+          <t>265319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>317338</t>
+          <t>315830</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>473573</t>
+          <t>469734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>555243</t>
+          <t>553028</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>582971</t>
+          <t>583146</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>676205</t>
+          <t>679166</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1077061</t>
+          <t>1083303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1201718</t>
+          <t>1215326</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2839107</t>
+          <t>2841322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2920777</t>
+          <t>2924616</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2868337</t>
+          <t>2865376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2961571</t>
+          <t>2961396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5737174</t>
+          <t>5723566</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5861831</t>
+          <t>5855589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399818</t>
+          <t>404957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399134</t>
+          <t>393355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310680</t>
+          <t>359462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303684</t>
+          <t>351375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710498</t>
+          <t>764419</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702986</t>
+          <t>752693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712633</t>
+          <t>769284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,17 +10043,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>418727</t>
+          <t>466989</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>455959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422020</t>
+          <t>472934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506843</t>
+          <t>496510</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500088</t>
+          <t>489801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510000</t>
+          <t>499239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>925570</t>
+          <t>963499</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>918230</t>
+          <t>950977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930631</t>
+          <t>970688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,67 +10351,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14479</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21360</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13206</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8435</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20361</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>37934</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45698</t>
+          <t>51707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -10464,67 +10464,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>515353</t>
+          <t>595036</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504707</t>
+          <t>581693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522711</t>
+          <t>603710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>607009</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>600128</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>612367</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>97,67%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>528593</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>521438</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>533364</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1043946</t>
+          <t>1202045</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031259</t>
+          <t>1188272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053914</t>
+          <t>1212860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535158</t>
+          <t>618491</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535158</t>
+          <t>618491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535158</t>
+          <t>618491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076957</t>
+          <t>1239979</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076957</t>
+          <t>1239979</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076957</t>
+          <t>1239979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>107153</t>
+          <t>112212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47351</t>
+          <t>95283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157714</t>
+          <t>134488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90785</t>
+          <t>93512</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>78174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111179</t>
+          <t>107507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>197938</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124341</t>
+          <t>180535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248081</t>
+          <t>232009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>780633</t>
+          <t>588405</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>730072</t>
+          <t>566129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>840435</t>
+          <t>605334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>621713</t>
+          <t>642983</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601319</t>
+          <t>628988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>637947</t>
+          <t>658321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1402347</t>
+          <t>1231388</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1352204</t>
+          <t>1205103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1475944</t>
+          <t>1256577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>165505</t>
+          <t>174194</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144872</t>
+          <t>155022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>196377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>142973</t>
+          <t>162260</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128920</t>
+          <t>145782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159729</t>
+          <t>179922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>308478</t>
+          <t>336454</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284496</t>
+          <t>309104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>337185</t>
+          <t>362329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>394732</t>
+          <t>434165</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374390</t>
+          <t>411982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>415365</t>
+          <t>453337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>401136</t>
+          <t>443830</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>384380</t>
+          <t>426168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415189</t>
+          <t>460308</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>795868</t>
+          <t>877995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>767161</t>
+          <t>852120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>819850</t>
+          <t>905345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544109</t>
+          <t>606090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544109</t>
+          <t>606090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544109</t>
+          <t>606090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104346</t>
+          <t>1214449</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104346</t>
+          <t>1214449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104346</t>
+          <t>1214449</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>169863</t>
+          <t>184926</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154093</t>
+          <t>167560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>185824</t>
+          <t>201999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>391476</t>
+          <t>205743</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>276067</t>
+          <t>190387</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>525104</t>
+          <t>221553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>561340</t>
+          <t>390669</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>441921</t>
+          <t>368728</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>766957</t>
+          <t>415343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>196227</t>
+          <t>219721</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180266</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211997</t>
+          <t>237087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>215705</t>
+          <t>232209</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82077</t>
+          <t>216399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331114</t>
+          <t>247565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>411931</t>
+          <t>451930</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206314</t>
+          <t>427256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531350</t>
+          <t>473871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366090</t>
+          <t>404647</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366090</t>
+          <t>404647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366090</t>
+          <t>404647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607181</t>
+          <t>437952</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607181</t>
+          <t>437952</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607181</t>
+          <t>437952</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973271</t>
+          <t>842599</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973271</t>
+          <t>842599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973271</t>
+          <t>842599</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>153937</t>
+          <t>167746</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140494</t>
+          <t>154820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166808</t>
+          <t>182646</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>274357</t>
+          <t>297491</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259886</t>
+          <t>280078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288691</t>
+          <t>311880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>428294</t>
+          <t>465238</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408056</t>
+          <t>444916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>448642</t>
+          <t>486521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>128822</t>
+          <t>142452</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115951</t>
+          <t>127552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142265</t>
+          <t>155378</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>150548</t>
+          <t>166148</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136214</t>
+          <t>151759</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165019</t>
+          <t>183561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>279370</t>
+          <t>308600</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>259022</t>
+          <t>287317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299608</t>
+          <t>328922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>463639</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>463639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424905</t>
+          <t>463639</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>773838</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>773838</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>773838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>621253</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>483909</t>
+          <t>632575</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>689114</t>
+          <t>724668</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>919978</t>
+          <t>781108</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>742025</t>
+          <t>740525</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1477015</t>
+          <t>822721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1541231</t>
+          <t>1456378</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1335900</t>
+          <t>1398603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2124866</t>
+          <t>1516704</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2834312</t>
+          <t>2851727</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2766451</t>
+          <t>2802329</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2971656</t>
+          <t>2894422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2735218</t>
+          <t>2948152</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2178181</t>
+          <t>2906539</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2913171</t>
+          <t>2988735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5569530</t>
+          <t>5799878</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4985895</t>
+          <t>5739552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5774861</t>
+          <t>5857653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
